--- a/ZonasEscolares/excels/LIMA-BARRANCA-BARRANCA.xlsx
+++ b/ZonasEscolares/excels/LIMA-BARRANCA-BARRANCA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-BARRANCA-BARRANCA.xlsx
+++ b/ZonasEscolares/excels/LIMA-BARRANCA-BARRANCA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>HOGAR DE SANTA ROSA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-10.75427</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.76673</v>
-      </c>
-      <c r="I2" t="n">
-        <v>244</v>
-      </c>
-      <c r="J2" t="n">
-        <v>30</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-10.75427</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.76673</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>322</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-10.74921</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.765272</v>
-      </c>
-      <c r="I3" t="n">
-        <v>405</v>
-      </c>
-      <c r="J3" t="n">
-        <v>18</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-10.74921</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.765272</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>370</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-10.75885</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.76036999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>259</v>
-      </c>
-      <c r="J4" t="n">
-        <v>16</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-10.75885</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.76037</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>446</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-10.749237</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.75770199999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>314</v>
-      </c>
-      <c r="J5" t="n">
-        <v>13</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-10.749237</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.757702</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>656</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-10.74598</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.75726</v>
-      </c>
-      <c r="I6" t="n">
-        <v>241</v>
-      </c>
-      <c r="J6" t="n">
-        <v>10</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-10.74598</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.75726</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>20475</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-10.75142</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.75748</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1492</v>
-      </c>
-      <c r="J7" t="n">
-        <v>64</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-10.75142</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.75748</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1492</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>20478</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-10.74564</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.75734</v>
-      </c>
-      <c r="I8" t="n">
-        <v>604</v>
-      </c>
-      <c r="J8" t="n">
-        <v>27</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-10.74564</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.75734</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>20480 SANTA CATALINA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-10.739353</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.771158</v>
-      </c>
-      <c r="I9" t="n">
-        <v>238</v>
-      </c>
-      <c r="J9" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-10.739353</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.771158</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>20528 VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-10.745031</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.761376</v>
-      </c>
-      <c r="I10" t="n">
-        <v>233</v>
-      </c>
-      <c r="J10" t="n">
-        <v>11</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-10.745031</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.761376</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>20947</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-10.691987</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.678664</v>
-      </c>
-      <c r="I11" t="n">
-        <v>228</v>
-      </c>
-      <c r="J11" t="n">
-        <v>10</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-10.691987</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.678664</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>21011 VIRGEN DE LOURDES</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-10.75592</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.76392</v>
-      </c>
-      <c r="I12" t="n">
-        <v>938</v>
-      </c>
-      <c r="J12" t="n">
-        <v>43</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-10.75592</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.76392</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>21012</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-10.75461</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.76367</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1150</v>
-      </c>
-      <c r="J13" t="n">
-        <v>48</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-10.75461</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.76367</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>21572 MICAELA BASTIDAS</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-10.690114</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.69215</v>
-      </c>
-      <c r="I14" t="n">
-        <v>439</v>
-      </c>
-      <c r="J14" t="n">
-        <v>28</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-10.690114</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.69215</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>21581 DECISION CAMPESINA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-10.740949</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.76578499999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>862</v>
-      </c>
-      <c r="J15" t="n">
-        <v>48</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-10.740949</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.765785</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>21606 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-10.71432</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.74094700000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>214</v>
-      </c>
-      <c r="J16" t="n">
-        <v>22</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-10.71432</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.740947</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>20854 GRAL. JUAN VELASCO ALVARADO</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-10.7287</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.71997</v>
-      </c>
-      <c r="I17" t="n">
-        <v>608</v>
-      </c>
-      <c r="J17" t="n">
-        <v>34</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-10.7287</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.71997</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>GUILLERMO E. BILLINGHURST</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-10.76063</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.75883</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1104</v>
-      </c>
-      <c r="J18" t="n">
-        <v>55</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-10.76063</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.75883</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>VENTURA CCALAMAQUI</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-10.75217</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.75735</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2270</v>
-      </c>
-      <c r="J19" t="n">
-        <v>119</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-10.75217</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.75735</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2270</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>21571 RICARDO PALMA SORIANO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-10.673758</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.62500900000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>248</v>
-      </c>
-      <c r="J20" t="n">
-        <v>17</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-10.673758</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.625009</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-10.7477</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.758443</v>
-      </c>
-      <c r="I21" t="n">
-        <v>40</v>
-      </c>
-      <c r="J21" t="n">
-        <v>6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-10.7477</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.758443</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>SAN MARTIN DE PORRAS / SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-10.757038</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.76079799999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>715</v>
-      </c>
-      <c r="J22" t="n">
-        <v>36</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-10.757038</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.760798</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>SAN AGUSTIN</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-10.7574</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.76394000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>342</v>
-      </c>
-      <c r="J23" t="n">
-        <v>15</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-10.7574</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.76394</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>LAS PALMAS NUEVA ESPERANZA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-10.75704</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.76148999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>221</v>
-      </c>
-      <c r="J24" t="n">
-        <v>28</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-10.75704</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.76149</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>VILLA MARIA</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-10.74719</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.75443</v>
-      </c>
-      <c r="I25" t="n">
-        <v>578</v>
-      </c>
-      <c r="J25" t="n">
-        <v>34</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-10.74719</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.75443</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>FE Y ALEGRIA 35</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-10.74568</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.75192</v>
-      </c>
-      <c r="I26" t="n">
-        <v>919</v>
-      </c>
-      <c r="J26" t="n">
-        <v>44</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-10.74568</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.75192</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>919</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-10.673832</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.811688</v>
-      </c>
-      <c r="I27" t="n">
-        <v>557</v>
-      </c>
-      <c r="J27" t="n">
-        <v>28</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-10.673832</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.811688</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>392 SEÑOR DE LUREN</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-10.804479</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.713689</v>
-      </c>
-      <c r="I28" t="n">
-        <v>234</v>
-      </c>
-      <c r="J28" t="n">
-        <v>13</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-10.804479</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.713689</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>20520</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-10.799957</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-77.71101400000001</v>
-      </c>
-      <c r="I29" t="n">
-        <v>373</v>
-      </c>
-      <c r="J29" t="n">
-        <v>16</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-10.799957</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-77.711014</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>20521</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-10.801645</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.711755</v>
-      </c>
-      <c r="I30" t="n">
-        <v>200</v>
-      </c>
-      <c r="J30" t="n">
-        <v>10</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-10.801645</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.711755</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>20523 CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-10.796469</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-77.712182</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1284</v>
-      </c>
-      <c r="J31" t="n">
-        <v>53</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-10.796469</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-77.712182</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>DIVINO CORAZON DE JESUS DE BARRANCA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-10.761384</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.755635</v>
-      </c>
-      <c r="I32" t="n">
-        <v>216</v>
-      </c>
-      <c r="J32" t="n">
-        <v>18</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-10.761384</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.755635</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-10.75527</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-77.75745999999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>678</v>
-      </c>
-      <c r="J33" t="n">
-        <v>36</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-10.75527</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-77.75746</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>EL BUEN PASTOR</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-10.752627</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-77.764201</v>
-      </c>
-      <c r="I34" t="n">
-        <v>619</v>
-      </c>
-      <c r="J34" t="n">
-        <v>16</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-10.752627</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-77.764201</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>BERTOLT BRECHT</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-10.75834</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-77.75761</v>
-      </c>
-      <c r="I35" t="n">
-        <v>701</v>
-      </c>
-      <c r="J35" t="n">
-        <v>33</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-10.75834</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-77.75761</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>ISAAC NEWTON SCHOOL</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-10.75625</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-77.76099000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>547</v>
-      </c>
-      <c r="J36" t="n">
-        <v>26</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-10.75625</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-77.76099</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>CORAZON DE MARIA</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-10.744301</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-77.752837</v>
-      </c>
-      <c r="I37" t="n">
-        <v>422</v>
-      </c>
-      <c r="J37" t="n">
-        <v>36</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-10.744301</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-77.752837</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-10.672546</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-77.820427</v>
-      </c>
-      <c r="I38" t="n">
-        <v>233</v>
-      </c>
-      <c r="J38" t="n">
-        <v>21</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-10.672546</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-77.820427</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-BARRANCA-BARRANCA.xlsx
+++ b/ZonasEscolares/excels/LIMA-BARRANCA-BARRANCA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>340556</t>
+          <t>348760</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HOGAR DE SANTA ROSA</t>
+          <t>656</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-10.75427</t>
+          <t>-10.74598</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.76673</t>
+          <t>-77.75726</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>241</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>348717</t>
+          <t>348897</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>20947</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-10.74921</t>
+          <t>-10.691987</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.765272</t>
+          <t>-77.678664</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>228</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>348722</t>
+          <t>350102</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>20521</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-10.75885</t>
+          <t>-10.801645</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.76037</t>
+          <t>-77.711755</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>348736</t>
+          <t>348864</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>20528 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-10.749237</t>
+          <t>-10.745031</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.757702</t>
+          <t>-77.761376</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>348760</t>
+          <t>349000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>VENTURA CCALAMAQUI</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-10.74598</t>
+          <t>-10.75217</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.75726</t>
+          <t>-77.75735</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>119</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>348802</t>
+          <t>348736</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20475</t>
+          <t>446</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-10.75142</t>
+          <t>-10.749237</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.75748</t>
+          <t>-77.757702</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>314</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>348821</t>
+          <t>349986</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>392 SEÑOR DE LUREN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-10.74564</t>
+          <t>-10.804479</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.75734</t>
+          <t>-77.713689</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>348835</t>
+          <t>349104</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20480 SANTA CATALINA</t>
+          <t>SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-10.739353</t>
+          <t>-10.7574</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.771158</t>
+          <t>-77.76394</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>342</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>348864</t>
+          <t>348722</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20528 VIRGEN DEL CARMEN</t>
+          <t>370</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-10.745031</t>
+          <t>-10.75885</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.761376</t>
+          <t>-77.76037</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>348897</t>
+          <t>350098</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20947</t>
+          <t>20520</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-10.691987</t>
+          <t>-10.799957</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.678664</t>
+          <t>-77.711014</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>373</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>348915</t>
+          <t>739382</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21011 VIRGEN DE LOURDES</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-10.75592</t>
+          <t>-10.752627</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.76392</t>
+          <t>-77.764201</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>619</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>348920</t>
+          <t>349019</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21012</t>
+          <t>21571 RICARDO PALMA SORIANO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-10.75461</t>
+          <t>-10.673758</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.76367</t>
+          <t>-77.625009</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>348944</t>
+          <t>348717</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>21572 MICAELA BASTIDAS</t>
+          <t>322</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-10.690114</t>
+          <t>-10.74921</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.69215</t>
+          <t>-77.765272</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>405</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>348958</t>
+          <t>739358</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>21581 DECISION CAMPESINA</t>
+          <t>DIVINO CORAZON DE JESUS DE BARRANCA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-10.740949</t>
+          <t>-10.761384</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.765785</t>
+          <t>-77.755635</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>348963</t>
+          <t>348835</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21606 FRANCISCO BOLOGNESI</t>
+          <t>20480 SANTA CATALINA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-10.71432</t>
+          <t>-10.739353</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.740947</t>
+          <t>-77.771158</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>348982</t>
+          <t>849762</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20854 GRAL. JUAN VELASCO ALVARADO</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-10.7287</t>
+          <t>-10.672546</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.71997</t>
+          <t>-77.820427</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>348996</t>
+          <t>348963</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GUILLERMO E. BILLINGHURST</t>
+          <t>21606 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-10.76063</t>
+          <t>-10.71432</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.75883</t>
+          <t>-77.740947</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>349000</t>
+          <t>829085</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VENTURA CCALAMAQUI</t>
+          <t>ISAAC NEWTON SCHOOL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-10.75217</t>
+          <t>-10.75625</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.75735</t>
+          <t>-77.76099</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>547</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>349019</t>
+          <t>348821</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>21571 RICARDO PALMA SORIANO</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-10.673758</t>
+          <t>-10.74564</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.625009</t>
+          <t>-77.75734</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>604</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>349076</t>
+          <t>348944</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VIRGEN DE FATIMA</t>
+          <t>21572 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-10.7477</t>
+          <t>-10.690114</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.758443</t>
+          <t>-77.69215</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>439</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>349081</t>
+          <t>349142</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRAS / SAN MARTIN DE PORRES</t>
+          <t>LAS PALMAS NUEVA ESPERANZA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-10.757038</t>
+          <t>-10.75704</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.760798</t>
+          <t>-77.76149</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>349104</t>
+          <t>349528</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN</t>
+          <t>MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-10.7574</t>
+          <t>-10.673832</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.76394</t>
+          <t>-77.811688</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>557</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>349142</t>
+          <t>340556</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LAS PALMAS NUEVA ESPERANZA</t>
+          <t>HOGAR DE SANTA ROSA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-10.75704</t>
+          <t>-10.75427</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.76149</t>
+          <t>-77.76673</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>244</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>349161</t>
+          <t>739400</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VILLA MARIA</t>
+          <t>BERTOLT BRECHT</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-10.74719</t>
+          <t>-10.75834</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.75443</t>
+          <t>-77.75761</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>701</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>349203</t>
+          <t>348982</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 35</t>
+          <t>20854 GRAL. JUAN VELASCO ALVARADO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-10.74568</t>
+          <t>-10.7287</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.75192</t>
+          <t>-77.71997</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>608</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>349528</t>
+          <t>349161</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU</t>
+          <t>VILLA MARIA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-10.673832</t>
+          <t>-10.74719</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.811688</t>
+          <t>-77.75443</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>578</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>349986</t>
+          <t>349081</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>392 SEÑOR DE LUREN</t>
+          <t>SAN MARTIN DE PORRAS / SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-10.804479</t>
+          <t>-10.757038</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.713689</t>
+          <t>-77.760798</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>715</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>350098</t>
+          <t>739377</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20520</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-10.799957</t>
+          <t>-10.75527</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.711014</t>
+          <t>-77.75746</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>678</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>350102</t>
+          <t>829090</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20521</t>
+          <t>CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-10.801645</t>
+          <t>-10.744301</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.711755</t>
+          <t>-77.752837</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>422</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>350121</t>
+          <t>348915</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20523 CORAZON DE JESUS</t>
+          <t>21011 VIRGEN DE LOURDES</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-10.796469</t>
+          <t>-10.75592</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.712182</t>
+          <t>-77.76392</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>938</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>739358</t>
+          <t>349203</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>DIVINO CORAZON DE JESUS DE BARRANCA</t>
+          <t>FE Y ALEGRIA 35</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-10.761384</t>
+          <t>-10.74568</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.755635</t>
+          <t>-77.75192</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>919</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>739377</t>
+          <t>348920</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>21012</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-10.75527</t>
+          <t>-10.75461</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.75746</t>
+          <t>-77.76367</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>739382</t>
+          <t>348958</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>21581 DECISION CAMPESINA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-10.752627</t>
+          <t>-10.740949</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.764201</t>
+          <t>-77.765785</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>862</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>739400</t>
+          <t>350121</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BERTOLT BRECHT</t>
+          <t>20523 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-10.75834</t>
+          <t>-10.796469</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.75761</t>
+          <t>-77.712182</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>829085</t>
+          <t>348996</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON SCHOOL</t>
+          <t>GUILLERMO E. BILLINGHURST</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-10.75625</t>
+          <t>-10.76063</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.76099</t>
+          <t>-77.75883</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,37 +2671,37 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>829090</t>
+          <t>349076</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CORAZON DE MARIA</t>
+          <t>VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-10.744301</t>
+          <t>-10.7477</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.752837</t>
+          <t>-77.758443</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>849762</t>
+          <t>348802</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>20475</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-10.672546</t>
+          <t>-10.75142</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.820427</t>
+          <t>-77.75748</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-BARRANCA-BARRANCA.xlsx
+++ b/ZonasEscolares/excels/LIMA-BARRANCA-BARRANCA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>348760</t>
+          <t>849762</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-10.74598</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.75726</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>-10.672546</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.820427</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>348897</t>
+          <t>829090</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20947</t>
+          <t>CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-10.691987</t>
+          <t>422</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.678664</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>-10.744301</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.752837</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>350102</t>
+          <t>829085</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20521</t>
+          <t>ISAAC NEWTON SCHOOL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-10.801645</t>
+          <t>547</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.711755</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-10.75625</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.76099</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>348864</t>
+          <t>739400</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20528 VIRGEN DEL CARMEN</t>
+          <t>BERTOLT BRECHT</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-10.745031</t>
+          <t>701</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.761376</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-10.75834</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.75761</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>349000</t>
+          <t>739382</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VENTURA CCALAMAQUI</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-10.75217</t>
+          <t>619</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.75735</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>-10.752627</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>-77.764201</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>348736</t>
+          <t>739377</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-10.749237</t>
+          <t>678</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.757702</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>-10.75527</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.75746</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>349986</t>
+          <t>739358</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>392 SEÑOR DE LUREN</t>
+          <t>DIVINO CORAZON DE JESUS DE BARRANCA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-10.804479</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.713689</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-10.761384</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.755635</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>349104</t>
+          <t>350121</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN</t>
+          <t>20523 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-10.7574</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.76394</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>-10.796469</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.712182</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>348722</t>
+          <t>350102</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>20521</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-10.75885</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.76037</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-10.801645</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.711755</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1069,22 +1069,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>-10.799957</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>-77.711014</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>739382</t>
+          <t>349986</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>392 SEÑOR DE LUREN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-10.752627</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.764201</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>-10.804479</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.713689</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>349019</t>
+          <t>349528</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21571 RICARDO PALMA SORIANO</t>
+          <t>MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-10.673758</t>
+          <t>557</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.625009</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>-10.673832</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.811688</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>348717</t>
+          <t>349203</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>FE Y ALEGRIA 35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-10.74921</t>
+          <t>919</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.765272</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>-10.74568</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.75192</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>739358</t>
+          <t>349161</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DIVINO CORAZON DE JESUS DE BARRANCA</t>
+          <t>VILLA MARIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-10.761384</t>
+          <t>578</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.755635</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>-10.74719</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.75443</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>348835</t>
+          <t>349142</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20480 SANTA CATALINA</t>
+          <t>LAS PALMAS NUEVA ESPERANZA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-10.739353</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.771158</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-10.75704</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.76149</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>849762</t>
+          <t>349104</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-10.672546</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.820427</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-10.7574</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.76394</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>348963</t>
+          <t>349081</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21606 FRANCISCO BOLOGNESI</t>
+          <t>SAN MARTIN DE PORRAS / SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-10.71432</t>
+          <t>715</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.740947</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>-10.757038</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.760798</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>829085</t>
+          <t>349076</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON SCHOOL</t>
+          <t>VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-10.75625</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.76099</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>-10.7477</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.758443</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>348821</t>
+          <t>349019</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>21571 RICARDO PALMA SORIANO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-10.74564</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.75734</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>-10.673758</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.625009</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>348944</t>
+          <t>349000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>21572 MICAELA BASTIDAS</t>
+          <t>VENTURA CCALAMAQUI</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-10.690114</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.69215</t>
+          <t>119</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>-10.75217</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.75735</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>349142</t>
+          <t>348996</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LAS PALMAS NUEVA ESPERANZA</t>
+          <t>GUILLERMO E. BILLINGHURST</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-10.75704</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.76149</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-10.76063</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.75883</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>349528</t>
+          <t>348982</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU</t>
+          <t>20854 GRAL. JUAN VELASCO ALVARADO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-10.673832</t>
+          <t>608</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.811688</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>-10.7287</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.71997</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>340556</t>
+          <t>348963</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HOGAR DE SANTA ROSA</t>
+          <t>21606 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-10.75427</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.76673</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>-10.71432</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.740947</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>739400</t>
+          <t>348958</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BERTOLT BRECHT</t>
+          <t>21581 DECISION CAMPESINA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-10.75834</t>
+          <t>862</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.75761</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>-10.740949</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.765785</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>348982</t>
+          <t>348944</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20854 GRAL. JUAN VELASCO ALVARADO</t>
+          <t>21572 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-10.7287</t>
+          <t>439</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.71997</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>-10.690114</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.69215</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>349161</t>
+          <t>348920</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>VILLA MARIA</t>
+          <t>21012</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-10.74719</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.75443</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>-10.75461</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.76367</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>349081</t>
+          <t>348915</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRAS / SAN MARTIN DE PORRES</t>
+          <t>21011 VIRGEN DE LOURDES</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-10.757038</t>
+          <t>938</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.760798</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>-10.75592</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.76392</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>739377</t>
+          <t>348897</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>20947</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-10.75527</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.75746</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>-10.691987</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.678664</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>829090</t>
+          <t>348864</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CORAZON DE MARIA</t>
+          <t>20528 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-10.744301</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.752837</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>-10.745031</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.761376</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>348915</t>
+          <t>348835</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>21011 VIRGEN DE LOURDES</t>
+          <t>20480 SANTA CATALINA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-10.75592</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.76392</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>-10.739353</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-77.771158</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>349203</t>
+          <t>348821</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 35</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-10.74568</t>
+          <t>604</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.75192</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>-10.74564</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-77.75734</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>348920</t>
+          <t>348802</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>21012</t>
+          <t>20475</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-10.75461</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.76367</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>-10.75142</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-77.75748</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>348958</t>
+          <t>348760</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>21581 DECISION CAMPESINA</t>
+          <t>656</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-10.740949</t>
+          <t>241</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.765785</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>-10.74598</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-77.75726</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>350121</t>
+          <t>348736</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20523 CORAZON DE JESUS</t>
+          <t>446</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-10.796469</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.712182</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>-10.749237</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-77.757702</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>348996</t>
+          <t>348722</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GUILLERMO E. BILLINGHURST</t>
+          <t>370</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-10.76063</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.75883</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>-10.75885</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-77.76037</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,37 +2671,37 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>349076</t>
+          <t>348717</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>VIRGEN DE FATIMA</t>
+          <t>322</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-10.7477</t>
+          <t>405</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.758443</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-10.74921</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-77.765272</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>348802</t>
+          <t>340556</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20475</t>
+          <t>HOGAR DE SANTA ROSA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-10.75142</t>
+          <t>244</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.75748</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>-10.75427</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-77.76673</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-BARRANCA-BARRANCA.xlsx
+++ b/ZonasEscolares/excels/LIMA-BARRANCA-BARRANCA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
